--- a/JCFD Fire Calls - Dashboard v1.xlsx
+++ b/JCFD Fire Calls - Dashboard v1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hbhklaw-my.sharepoint.com/personal/king_hbhklaw_com/Documents/Documents/Jordans Chapel VFD/jcfd-dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hbhklaw-my.sharepoint.com/personal/king_hbhklaw_com/Documents/Downloads/jcfd_streamlit_app/jcfd_streamlit_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02908EFB-1241-4151-BB84-5E30A49FADCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{02908EFB-1241-4151-BB84-5E30A49FADCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7E0DC0A-EBC1-4266-844D-17FCD0C39535}"/>
   <bookViews>
-    <workbookView xWindow="-11610" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="492">
   <si>
     <t>Date</t>
   </si>
@@ -1459,40 +1459,43 @@
     <t>Fire Alarm</t>
   </si>
   <si>
-    <t>Motor Vehicle Collision</t>
-  </si>
-  <si>
-    <t>Service / Investigation</t>
-  </si>
-  <si>
-    <t>Outside / Brush Fire</t>
-  </si>
-  <si>
     <t>Structure Fire</t>
   </si>
   <si>
-    <t>Medical / EMS Assist</t>
-  </si>
-  <si>
     <t>HazMat / Gas Leak</t>
   </si>
   <si>
-    <t>Vehicle/Equipment Fire</t>
-  </si>
-  <si>
     <t>Electrical Hazard</t>
   </si>
   <si>
-    <t>Mutual/Auto Aid (Unspecified)</t>
-  </si>
-  <si>
     <t>S US Hwy 13</t>
   </si>
   <si>
-    <t>NC Highway 55</t>
-  </si>
-  <si>
-    <t>US Highway 13 S</t>
+    <t>Hwy 13</t>
+  </si>
+  <si>
+    <t>Hwy 55</t>
+  </si>
+  <si>
+    <t>MVC</t>
+  </si>
+  <si>
+    <t>Brush Fire</t>
+  </si>
+  <si>
+    <t>EMS</t>
+  </si>
+  <si>
+    <t>Investigation</t>
+  </si>
+  <si>
+    <t>Investigate</t>
+  </si>
+  <si>
+    <t>Vehicle/Equip Fire</t>
+  </si>
+  <si>
+    <t>Mutual Aid - Unspecified</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1887,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C2" t="s">
         <v>478</v>
@@ -1898,7 +1901,7 @@
         <v>365</v>
       </c>
       <c r="C3" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1906,10 +1909,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C4" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1920,7 +1923,7 @@
         <v>360</v>
       </c>
       <c r="C5" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -1942,7 +1945,7 @@
         <v>362</v>
       </c>
       <c r="C7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -1953,7 +1956,7 @@
         <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1961,10 +1964,10 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C9" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -1975,7 +1978,7 @@
         <v>363</v>
       </c>
       <c r="C10" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -1986,7 +1989,7 @@
         <v>364</v>
       </c>
       <c r="C11" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -1997,7 +2000,7 @@
         <v>364</v>
       </c>
       <c r="C12" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -2008,7 +2011,7 @@
         <v>365</v>
       </c>
       <c r="C13" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -2019,7 +2022,7 @@
         <v>365</v>
       </c>
       <c r="C14" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -2030,7 +2033,7 @@
         <v>366</v>
       </c>
       <c r="C15" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -2041,7 +2044,7 @@
         <v>367</v>
       </c>
       <c r="C16" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -2049,10 +2052,10 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C17" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -2060,10 +2063,10 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
+        <v>483</v>
+      </c>
+      <c r="C18" t="s">
         <v>490</v>
-      </c>
-      <c r="C18" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -2074,7 +2077,7 @@
         <v>368</v>
       </c>
       <c r="C19" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -2085,7 +2088,7 @@
         <v>369</v>
       </c>
       <c r="C20" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -2107,7 +2110,7 @@
         <v>371</v>
       </c>
       <c r="C22" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -2118,7 +2121,7 @@
         <v>372</v>
       </c>
       <c r="C23" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -2129,7 +2132,7 @@
         <v>373</v>
       </c>
       <c r="C24" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -2140,7 +2143,7 @@
         <v>364</v>
       </c>
       <c r="C25" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -2148,7 +2151,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C26" t="s">
         <v>478</v>
@@ -2170,7 +2173,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C28" t="s">
         <v>478</v>
@@ -2181,10 +2184,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C29" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -2195,7 +2198,7 @@
         <v>374</v>
       </c>
       <c r="C30" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -2203,7 +2206,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C31" t="s">
         <v>478</v>
@@ -2214,10 +2217,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C32" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -2228,7 +2231,7 @@
         <v>375</v>
       </c>
       <c r="C33" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -2236,10 +2239,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C34" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -2250,7 +2253,7 @@
         <v>376</v>
       </c>
       <c r="C35" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -2261,7 +2264,7 @@
         <v>377</v>
       </c>
       <c r="C36" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -2269,7 +2272,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C37" t="s">
         <v>478</v>
@@ -2294,7 +2297,7 @@
         <v>364</v>
       </c>
       <c r="C39" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -2338,7 +2341,7 @@
         <v>365</v>
       </c>
       <c r="C43" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -2346,10 +2349,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C44" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -2357,10 +2360,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C45" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -2371,7 +2374,7 @@
         <v>365</v>
       </c>
       <c r="C46" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -2379,7 +2382,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C47" t="s">
         <v>478</v>
@@ -2390,10 +2393,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
+        <v>484</v>
+      </c>
+      <c r="C48" t="s">
         <v>489</v>
-      </c>
-      <c r="C48" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -2404,7 +2407,7 @@
         <v>380</v>
       </c>
       <c r="C49" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -2415,7 +2418,7 @@
         <v>377</v>
       </c>
       <c r="C50" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -2426,7 +2429,7 @@
         <v>381</v>
       </c>
       <c r="C51" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -2437,7 +2440,7 @@
         <v>382</v>
       </c>
       <c r="C52" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -2459,7 +2462,7 @@
         <v>383</v>
       </c>
       <c r="C54" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -2481,7 +2484,7 @@
         <v>364</v>
       </c>
       <c r="C56" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -2489,10 +2492,10 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C57" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -2503,7 +2506,7 @@
         <v>384</v>
       </c>
       <c r="C58" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -2514,7 +2517,7 @@
         <v>366</v>
       </c>
       <c r="C59" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -2522,10 +2525,10 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C60" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -2536,7 +2539,7 @@
         <v>385</v>
       </c>
       <c r="C61" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -2547,7 +2550,7 @@
         <v>378</v>
       </c>
       <c r="C62" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -2555,10 +2558,10 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C63" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -2569,7 +2572,7 @@
         <v>386</v>
       </c>
       <c r="C64" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -2577,7 +2580,7 @@
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C65" t="s">
         <v>478</v>
@@ -2591,7 +2594,7 @@
         <v>387</v>
       </c>
       <c r="C66" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -2599,10 +2602,10 @@
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C67" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
@@ -2613,7 +2616,7 @@
         <v>388</v>
       </c>
       <c r="C68" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -2624,7 +2627,7 @@
         <v>368</v>
       </c>
       <c r="C69" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -2635,7 +2638,7 @@
         <v>386</v>
       </c>
       <c r="C70" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -2646,7 +2649,7 @@
         <v>359</v>
       </c>
       <c r="C71" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -2654,10 +2657,10 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C72" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -2665,10 +2668,10 @@
         <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C73" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
@@ -2679,7 +2682,7 @@
         <v>389</v>
       </c>
       <c r="C74" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
@@ -2687,10 +2690,10 @@
         <v>69</v>
       </c>
       <c r="B75" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C75" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
@@ -2698,7 +2701,7 @@
         <v>70</v>
       </c>
       <c r="B76" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C76" t="s">
         <v>478</v>
@@ -2712,7 +2715,7 @@
         <v>364</v>
       </c>
       <c r="C77" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
@@ -2723,7 +2726,7 @@
         <v>364</v>
       </c>
       <c r="C78" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -2734,7 +2737,7 @@
         <v>390</v>
       </c>
       <c r="C79" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
@@ -2753,10 +2756,10 @@
         <v>75</v>
       </c>
       <c r="B81" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C81" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
@@ -2767,7 +2770,7 @@
         <v>391</v>
       </c>
       <c r="C82" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
@@ -2778,7 +2781,7 @@
         <v>392</v>
       </c>
       <c r="C83" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
@@ -2789,7 +2792,7 @@
         <v>406</v>
       </c>
       <c r="C84" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -2800,7 +2803,7 @@
         <v>360</v>
       </c>
       <c r="C85" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
@@ -2822,7 +2825,7 @@
         <v>394</v>
       </c>
       <c r="C87" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
@@ -2830,7 +2833,7 @@
         <v>81</v>
       </c>
       <c r="B88" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C88" t="s">
         <v>478</v>
@@ -2844,7 +2847,7 @@
         <v>394</v>
       </c>
       <c r="C89" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
@@ -2855,7 +2858,7 @@
         <v>395</v>
       </c>
       <c r="C90" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
@@ -2863,10 +2866,10 @@
         <v>83</v>
       </c>
       <c r="B91" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C91" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
@@ -2877,7 +2880,7 @@
         <v>396</v>
       </c>
       <c r="C92" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
@@ -2885,10 +2888,10 @@
         <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C93" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
@@ -2896,10 +2899,10 @@
         <v>86</v>
       </c>
       <c r="B94" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C94" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
@@ -2910,7 +2913,7 @@
         <v>360</v>
       </c>
       <c r="C95" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
@@ -2932,7 +2935,7 @@
         <v>365</v>
       </c>
       <c r="C97" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
@@ -2951,10 +2954,10 @@
         <v>90</v>
       </c>
       <c r="B99" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C99" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
@@ -2965,7 +2968,7 @@
         <v>368</v>
       </c>
       <c r="C100" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
@@ -2976,7 +2979,7 @@
         <v>367</v>
       </c>
       <c r="C101" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
@@ -2987,7 +2990,7 @@
         <v>397</v>
       </c>
       <c r="C102" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
@@ -2998,7 +3001,7 @@
         <v>383</v>
       </c>
       <c r="C103" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
@@ -3009,7 +3012,7 @@
         <v>398</v>
       </c>
       <c r="C104" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
@@ -3020,7 +3023,7 @@
         <v>399</v>
       </c>
       <c r="C105" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
@@ -3028,10 +3031,10 @@
         <v>97</v>
       </c>
       <c r="B106" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C106" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
@@ -3042,7 +3045,7 @@
         <v>400</v>
       </c>
       <c r="C107" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
@@ -3053,7 +3056,7 @@
         <v>401</v>
       </c>
       <c r="C108" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
@@ -3064,7 +3067,7 @@
         <v>402</v>
       </c>
       <c r="C109" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
@@ -3075,7 +3078,7 @@
         <v>403</v>
       </c>
       <c r="C110" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
@@ -3086,7 +3089,7 @@
         <v>404</v>
       </c>
       <c r="C111" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
@@ -3097,7 +3100,7 @@
         <v>404</v>
       </c>
       <c r="C112" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
@@ -3108,7 +3111,7 @@
         <v>405</v>
       </c>
       <c r="C113" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
@@ -3116,10 +3119,10 @@
         <v>104</v>
       </c>
       <c r="B114" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C114" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
@@ -3130,7 +3133,7 @@
         <v>403</v>
       </c>
       <c r="C115" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
@@ -3141,7 +3144,7 @@
         <v>382</v>
       </c>
       <c r="C116" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
@@ -3152,7 +3155,7 @@
         <v>406</v>
       </c>
       <c r="C117" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -3163,7 +3166,7 @@
         <v>364</v>
       </c>
       <c r="C118" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -3185,7 +3188,7 @@
         <v>400</v>
       </c>
       <c r="C120" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -3196,7 +3199,7 @@
         <v>365</v>
       </c>
       <c r="C121" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -3204,7 +3207,7 @@
         <v>111</v>
       </c>
       <c r="B122" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C122" t="s">
         <v>478</v>
@@ -3218,7 +3221,7 @@
         <v>407</v>
       </c>
       <c r="C123" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
@@ -3226,7 +3229,7 @@
         <v>113</v>
       </c>
       <c r="B124" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C124" t="s">
         <v>478</v>
@@ -3240,7 +3243,7 @@
         <v>398</v>
       </c>
       <c r="C125" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -3251,7 +3254,7 @@
         <v>408</v>
       </c>
       <c r="C126" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -3262,7 +3265,7 @@
         <v>368</v>
       </c>
       <c r="C127" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
@@ -3273,7 +3276,7 @@
         <v>367</v>
       </c>
       <c r="C128" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
@@ -3281,7 +3284,7 @@
         <v>117</v>
       </c>
       <c r="B129" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C129" t="s">
         <v>478</v>
@@ -3292,10 +3295,10 @@
         <v>118</v>
       </c>
       <c r="B130" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C130" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
@@ -3317,7 +3320,7 @@
         <v>409</v>
       </c>
       <c r="C132" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
@@ -3325,10 +3328,10 @@
         <v>121</v>
       </c>
       <c r="B133" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C133" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
@@ -3339,7 +3342,7 @@
         <v>410</v>
       </c>
       <c r="C134" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
@@ -3347,10 +3350,10 @@
         <v>123</v>
       </c>
       <c r="B135" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C135" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
@@ -3361,7 +3364,7 @@
         <v>411</v>
       </c>
       <c r="C136" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -3372,7 +3375,7 @@
         <v>403</v>
       </c>
       <c r="C137" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -3391,10 +3394,10 @@
         <v>127</v>
       </c>
       <c r="B139" t="s">
+        <v>483</v>
+      </c>
+      <c r="C139" t="s">
         <v>490</v>
-      </c>
-      <c r="C139" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -3405,7 +3408,7 @@
         <v>385</v>
       </c>
       <c r="C140" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -3416,7 +3419,7 @@
         <v>410</v>
       </c>
       <c r="C141" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -3438,7 +3441,7 @@
         <v>368</v>
       </c>
       <c r="C143" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -3449,7 +3452,7 @@
         <v>403</v>
       </c>
       <c r="C144" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -3457,10 +3460,10 @@
         <v>133</v>
       </c>
       <c r="B145" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C145" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
@@ -3482,7 +3485,7 @@
         <v>412</v>
       </c>
       <c r="C147" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -3490,10 +3493,10 @@
         <v>136</v>
       </c>
       <c r="B148" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C148" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -3504,7 +3507,7 @@
         <v>382</v>
       </c>
       <c r="C149" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -3515,7 +3518,7 @@
         <v>413</v>
       </c>
       <c r="C150" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -3526,7 +3529,7 @@
         <v>414</v>
       </c>
       <c r="C151" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -3537,7 +3540,7 @@
         <v>415</v>
       </c>
       <c r="C152" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -3548,7 +3551,7 @@
         <v>416</v>
       </c>
       <c r="C153" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -3559,7 +3562,7 @@
         <v>385</v>
       </c>
       <c r="C154" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -3570,7 +3573,7 @@
         <v>417</v>
       </c>
       <c r="C155" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -3581,7 +3584,7 @@
         <v>398</v>
       </c>
       <c r="C156" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -3592,7 +3595,7 @@
         <v>418</v>
       </c>
       <c r="C157" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -3603,7 +3606,7 @@
         <v>406</v>
       </c>
       <c r="C158" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -3611,10 +3614,10 @@
         <v>146</v>
       </c>
       <c r="B159" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C159" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -3622,10 +3625,10 @@
         <v>147</v>
       </c>
       <c r="B160" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C160" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -3636,7 +3639,7 @@
         <v>419</v>
       </c>
       <c r="C161" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -3644,10 +3647,10 @@
         <v>149</v>
       </c>
       <c r="B162" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C162" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -3658,7 +3661,7 @@
         <v>420</v>
       </c>
       <c r="C163" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -3669,7 +3672,7 @@
         <v>421</v>
       </c>
       <c r="C164" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -3680,7 +3683,7 @@
         <v>405</v>
       </c>
       <c r="C165" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -3691,7 +3694,7 @@
         <v>422</v>
       </c>
       <c r="C166" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -3702,7 +3705,7 @@
         <v>423</v>
       </c>
       <c r="C167" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
@@ -3724,7 +3727,7 @@
         <v>379</v>
       </c>
       <c r="C169" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
@@ -3735,7 +3738,7 @@
         <v>396</v>
       </c>
       <c r="C170" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
@@ -3746,7 +3749,7 @@
         <v>422</v>
       </c>
       <c r="C171" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
@@ -3757,7 +3760,7 @@
         <v>424</v>
       </c>
       <c r="C172" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -3768,7 +3771,7 @@
         <v>378</v>
       </c>
       <c r="C173" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
@@ -3776,7 +3779,7 @@
         <v>159</v>
       </c>
       <c r="B174" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C174" t="s">
         <v>478</v>
@@ -3790,7 +3793,7 @@
         <v>367</v>
       </c>
       <c r="C175" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
@@ -3801,7 +3804,7 @@
         <v>425</v>
       </c>
       <c r="C176" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
@@ -3812,7 +3815,7 @@
         <v>365</v>
       </c>
       <c r="C177" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
@@ -3842,10 +3845,10 @@
         <v>164</v>
       </c>
       <c r="B180" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C180" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
@@ -3856,7 +3859,7 @@
         <v>427</v>
       </c>
       <c r="C181" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
@@ -3867,7 +3870,7 @@
         <v>428</v>
       </c>
       <c r="C182" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
@@ -3878,7 +3881,7 @@
         <v>429</v>
       </c>
       <c r="C183" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
@@ -3889,7 +3892,7 @@
         <v>430</v>
       </c>
       <c r="C184" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
@@ -3900,7 +3903,7 @@
         <v>375</v>
       </c>
       <c r="C185" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
@@ -3911,7 +3914,7 @@
         <v>365</v>
       </c>
       <c r="C186" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
@@ -3922,7 +3925,7 @@
         <v>431</v>
       </c>
       <c r="C187" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
@@ -3933,7 +3936,7 @@
         <v>428</v>
       </c>
       <c r="C188" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
@@ -3944,7 +3947,7 @@
         <v>432</v>
       </c>
       <c r="C189" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
@@ -3955,7 +3958,7 @@
         <v>386</v>
       </c>
       <c r="C190" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
@@ -3963,10 +3966,10 @@
         <v>172</v>
       </c>
       <c r="B191" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C191" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -3977,7 +3980,7 @@
         <v>361</v>
       </c>
       <c r="C192" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
@@ -3988,7 +3991,7 @@
         <v>365</v>
       </c>
       <c r="C193" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
@@ -3999,7 +4002,7 @@
         <v>409</v>
       </c>
       <c r="C194" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
@@ -4010,7 +4013,7 @@
         <v>433</v>
       </c>
       <c r="C195" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
@@ -4043,7 +4046,7 @@
         <v>365</v>
       </c>
       <c r="C198" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
@@ -4054,7 +4057,7 @@
         <v>434</v>
       </c>
       <c r="C199" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
@@ -4062,7 +4065,7 @@
         <v>177</v>
       </c>
       <c r="B200" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C200" t="s">
         <v>478</v>
@@ -4076,7 +4079,7 @@
         <v>368</v>
       </c>
       <c r="C201" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
@@ -4087,7 +4090,7 @@
         <v>368</v>
       </c>
       <c r="C202" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
@@ -4098,7 +4101,7 @@
         <v>360</v>
       </c>
       <c r="C203" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
@@ -4109,7 +4112,7 @@
         <v>435</v>
       </c>
       <c r="C204" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -4128,7 +4131,7 @@
         <v>182</v>
       </c>
       <c r="B206" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C206" t="s">
         <v>478</v>
@@ -4139,7 +4142,7 @@
         <v>182</v>
       </c>
       <c r="B207" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C207" t="s">
         <v>478</v>
@@ -4150,7 +4153,7 @@
         <v>183</v>
       </c>
       <c r="B208" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C208" t="s">
         <v>478</v>
@@ -4161,7 +4164,7 @@
         <v>184</v>
       </c>
       <c r="B209" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C209" t="s">
         <v>478</v>
@@ -4172,10 +4175,10 @@
         <v>185</v>
       </c>
       <c r="B210" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C210" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
@@ -4183,10 +4186,10 @@
         <v>186</v>
       </c>
       <c r="B211" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C211" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
@@ -4194,7 +4197,7 @@
         <v>187</v>
       </c>
       <c r="B212" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C212" t="s">
         <v>478</v>
@@ -4208,7 +4211,7 @@
         <v>361</v>
       </c>
       <c r="C213" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
@@ -4216,7 +4219,7 @@
         <v>189</v>
       </c>
       <c r="B214" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C214" t="s">
         <v>478</v>
@@ -4227,7 +4230,7 @@
         <v>190</v>
       </c>
       <c r="B215" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C215" t="s">
         <v>478</v>
@@ -4238,7 +4241,7 @@
         <v>191</v>
       </c>
       <c r="B216" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C216" t="s">
         <v>478</v>
@@ -4249,7 +4252,7 @@
         <v>191</v>
       </c>
       <c r="B217" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C217" t="s">
         <v>478</v>
@@ -4260,7 +4263,7 @@
         <v>191</v>
       </c>
       <c r="B218" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C218" t="s">
         <v>478</v>
@@ -4296,7 +4299,7 @@
         <v>398</v>
       </c>
       <c r="C221" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
@@ -4307,7 +4310,7 @@
         <v>436</v>
       </c>
       <c r="C222" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
@@ -4318,7 +4321,7 @@
         <v>437</v>
       </c>
       <c r="C223" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
@@ -4329,7 +4332,7 @@
         <v>393</v>
       </c>
       <c r="C224" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
@@ -4340,7 +4343,7 @@
         <v>365</v>
       </c>
       <c r="C225" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
@@ -4351,7 +4354,7 @@
         <v>365</v>
       </c>
       <c r="C226" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
@@ -4362,7 +4365,7 @@
         <v>438</v>
       </c>
       <c r="C227" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
@@ -4384,7 +4387,7 @@
         <v>393</v>
       </c>
       <c r="C229" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
@@ -4395,7 +4398,7 @@
         <v>365</v>
       </c>
       <c r="C230" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
@@ -4403,10 +4406,10 @@
         <v>203</v>
       </c>
       <c r="B231" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C231" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
@@ -4428,7 +4431,7 @@
         <v>365</v>
       </c>
       <c r="C233" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
@@ -4447,10 +4450,10 @@
         <v>207</v>
       </c>
       <c r="B235" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C235" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
@@ -4461,7 +4464,7 @@
         <v>373</v>
       </c>
       <c r="C236" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
@@ -4472,7 +4475,7 @@
         <v>382</v>
       </c>
       <c r="C237" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
@@ -4494,7 +4497,7 @@
         <v>365</v>
       </c>
       <c r="C239" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
@@ -4502,7 +4505,7 @@
         <v>212</v>
       </c>
       <c r="B240" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C240" t="s">
         <v>478</v>
@@ -4571,7 +4574,7 @@
         <v>361</v>
       </c>
       <c r="C246" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
@@ -4579,10 +4582,10 @@
         <v>219</v>
       </c>
       <c r="B247" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C247" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
@@ -4593,7 +4596,7 @@
         <v>439</v>
       </c>
       <c r="C248" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
@@ -4615,7 +4618,7 @@
         <v>365</v>
       </c>
       <c r="C250" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
@@ -4637,7 +4640,7 @@
         <v>440</v>
       </c>
       <c r="C252" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
@@ -4670,7 +4673,7 @@
         <v>367</v>
       </c>
       <c r="C255" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
@@ -4681,7 +4684,7 @@
         <v>365</v>
       </c>
       <c r="C256" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
@@ -4692,7 +4695,7 @@
         <v>441</v>
       </c>
       <c r="C257" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
@@ -4703,7 +4706,7 @@
         <v>442</v>
       </c>
       <c r="C258" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
@@ -4725,7 +4728,7 @@
         <v>398</v>
       </c>
       <c r="C260" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
@@ -4736,7 +4739,7 @@
         <v>443</v>
       </c>
       <c r="C261" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
@@ -4747,7 +4750,7 @@
         <v>380</v>
       </c>
       <c r="C262" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
@@ -4758,7 +4761,7 @@
         <v>400</v>
       </c>
       <c r="C263" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
@@ -4791,7 +4794,7 @@
         <v>428</v>
       </c>
       <c r="C266" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
@@ -4821,10 +4824,10 @@
         <v>240</v>
       </c>
       <c r="B269" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C269" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
@@ -4835,7 +4838,7 @@
         <v>366</v>
       </c>
       <c r="C270" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
@@ -4846,7 +4849,7 @@
         <v>382</v>
       </c>
       <c r="C271" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
@@ -4857,7 +4860,7 @@
         <v>444</v>
       </c>
       <c r="C272" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
@@ -4865,10 +4868,10 @@
         <v>243</v>
       </c>
       <c r="B273" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C273" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
@@ -4890,7 +4893,7 @@
         <v>445</v>
       </c>
       <c r="C275" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
@@ -4901,7 +4904,7 @@
         <v>446</v>
       </c>
       <c r="C276" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
@@ -4912,7 +4915,7 @@
         <v>447</v>
       </c>
       <c r="C277" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
@@ -4920,10 +4923,10 @@
         <v>246</v>
       </c>
       <c r="B278" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C278" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
@@ -4934,7 +4937,7 @@
         <v>361</v>
       </c>
       <c r="C279" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
@@ -4942,10 +4945,10 @@
         <v>248</v>
       </c>
       <c r="B280" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C280" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
@@ -4956,7 +4959,7 @@
         <v>441</v>
       </c>
       <c r="C281" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
@@ -4967,7 +4970,7 @@
         <v>441</v>
       </c>
       <c r="C282" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
@@ -4989,7 +4992,7 @@
         <v>448</v>
       </c>
       <c r="C284" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
@@ -4997,10 +5000,10 @@
         <v>253</v>
       </c>
       <c r="B285" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C285" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
@@ -5011,7 +5014,7 @@
         <v>449</v>
       </c>
       <c r="C286" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
@@ -5022,7 +5025,7 @@
         <v>382</v>
       </c>
       <c r="C287" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
@@ -5033,7 +5036,7 @@
         <v>450</v>
       </c>
       <c r="C288" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
@@ -5044,7 +5047,7 @@
         <v>451</v>
       </c>
       <c r="C289" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
@@ -5055,7 +5058,7 @@
         <v>452</v>
       </c>
       <c r="C290" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
@@ -5077,7 +5080,7 @@
         <v>379</v>
       </c>
       <c r="C292" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
@@ -5088,7 +5091,7 @@
         <v>405</v>
       </c>
       <c r="C293" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
@@ -5099,7 +5102,7 @@
         <v>453</v>
       </c>
       <c r="C294" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
@@ -5110,7 +5113,7 @@
         <v>454</v>
       </c>
       <c r="C295" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
@@ -5121,7 +5124,7 @@
         <v>455</v>
       </c>
       <c r="C296" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
@@ -5140,10 +5143,10 @@
         <v>263</v>
       </c>
       <c r="B298" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C298" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
@@ -5154,7 +5157,7 @@
         <v>438</v>
       </c>
       <c r="C299" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
@@ -5165,7 +5168,7 @@
         <v>450</v>
       </c>
       <c r="C300" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
@@ -5173,7 +5176,7 @@
         <v>266</v>
       </c>
       <c r="B301" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C301" t="s">
         <v>478</v>
@@ -5187,7 +5190,7 @@
         <v>428</v>
       </c>
       <c r="C302" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
@@ -5198,7 +5201,7 @@
         <v>456</v>
       </c>
       <c r="C303" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
@@ -5209,7 +5212,7 @@
         <v>398</v>
       </c>
       <c r="C304" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
@@ -5220,7 +5223,7 @@
         <v>457</v>
       </c>
       <c r="C305" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
@@ -5231,7 +5234,7 @@
         <v>365</v>
       </c>
       <c r="C306" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
@@ -5242,7 +5245,7 @@
         <v>458</v>
       </c>
       <c r="C307" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
@@ -5253,7 +5256,7 @@
         <v>459</v>
       </c>
       <c r="C308" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
@@ -5264,7 +5267,7 @@
         <v>426</v>
       </c>
       <c r="C309" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
@@ -5275,7 +5278,7 @@
         <v>361</v>
       </c>
       <c r="C310" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
@@ -5283,10 +5286,10 @@
         <v>276</v>
       </c>
       <c r="B311" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C311" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
@@ -5297,7 +5300,7 @@
         <v>382</v>
       </c>
       <c r="C312" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
@@ -5308,7 +5311,7 @@
         <v>396</v>
       </c>
       <c r="C313" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
@@ -5319,7 +5322,7 @@
         <v>460</v>
       </c>
       <c r="C314" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
@@ -5327,10 +5330,10 @@
         <v>279</v>
       </c>
       <c r="B315" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C315" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
@@ -5341,7 +5344,7 @@
         <v>461</v>
       </c>
       <c r="C316" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
@@ -5349,10 +5352,10 @@
         <v>281</v>
       </c>
       <c r="B317" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C317" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
@@ -5360,10 +5363,10 @@
         <v>282</v>
       </c>
       <c r="B318" t="s">
+        <v>483</v>
+      </c>
+      <c r="C318" t="s">
         <v>490</v>
-      </c>
-      <c r="C318" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
@@ -5374,7 +5377,7 @@
         <v>365</v>
       </c>
       <c r="C319" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
@@ -5385,7 +5388,7 @@
         <v>365</v>
       </c>
       <c r="C320" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
@@ -5396,7 +5399,7 @@
         <v>361</v>
       </c>
       <c r="C321" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
@@ -5407,7 +5410,7 @@
         <v>462</v>
       </c>
       <c r="C322" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
@@ -5418,7 +5421,7 @@
         <v>463</v>
       </c>
       <c r="C323" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
@@ -5437,7 +5440,7 @@
         <v>289</v>
       </c>
       <c r="B325" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C325" t="s">
         <v>478</v>
@@ -5451,7 +5454,7 @@
         <v>379</v>
       </c>
       <c r="C326" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
@@ -5462,7 +5465,7 @@
         <v>385</v>
       </c>
       <c r="C327" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
@@ -5470,7 +5473,7 @@
         <v>292</v>
       </c>
       <c r="B328" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C328" t="s">
         <v>478</v>
@@ -5484,7 +5487,7 @@
         <v>464</v>
       </c>
       <c r="C329" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
@@ -5495,7 +5498,7 @@
         <v>465</v>
       </c>
       <c r="C330" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
@@ -5506,7 +5509,7 @@
         <v>466</v>
       </c>
       <c r="C331" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
@@ -5528,7 +5531,7 @@
         <v>398</v>
       </c>
       <c r="C333" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
@@ -5539,7 +5542,7 @@
         <v>361</v>
       </c>
       <c r="C334" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
@@ -5550,7 +5553,7 @@
         <v>426</v>
       </c>
       <c r="C335" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
@@ -5561,7 +5564,7 @@
         <v>363</v>
       </c>
       <c r="C336" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
@@ -5572,7 +5575,7 @@
         <v>365</v>
       </c>
       <c r="C337" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
@@ -5583,7 +5586,7 @@
         <v>373</v>
       </c>
       <c r="C338" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
@@ -5594,7 +5597,7 @@
         <v>467</v>
       </c>
       <c r="C339" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
@@ -5613,10 +5616,10 @@
         <v>304</v>
       </c>
       <c r="B341" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C341" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
@@ -5624,10 +5627,10 @@
         <v>305</v>
       </c>
       <c r="B342" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C342" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
@@ -5638,7 +5641,7 @@
         <v>450</v>
       </c>
       <c r="C343" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
@@ -5649,7 +5652,7 @@
         <v>468</v>
       </c>
       <c r="C344" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
@@ -5657,7 +5660,7 @@
         <v>308</v>
       </c>
       <c r="B345" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C345" t="s">
         <v>478</v>
@@ -5671,7 +5674,7 @@
         <v>469</v>
       </c>
       <c r="C346" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
@@ -5682,7 +5685,7 @@
         <v>368</v>
       </c>
       <c r="C347" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
@@ -5693,7 +5696,7 @@
         <v>365</v>
       </c>
       <c r="C348" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
@@ -5701,10 +5704,10 @@
         <v>311</v>
       </c>
       <c r="B349" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C349" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
@@ -5726,7 +5729,7 @@
         <v>416</v>
       </c>
       <c r="C351" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
@@ -5737,7 +5740,7 @@
         <v>365</v>
       </c>
       <c r="C352" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
@@ -5748,7 +5751,7 @@
         <v>380</v>
       </c>
       <c r="C353" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
@@ -5759,7 +5762,7 @@
         <v>470</v>
       </c>
       <c r="C354" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
@@ -5770,7 +5773,7 @@
         <v>448</v>
       </c>
       <c r="C355" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
@@ -5781,7 +5784,7 @@
         <v>367</v>
       </c>
       <c r="C356" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
@@ -5792,7 +5795,7 @@
         <v>471</v>
       </c>
       <c r="C357" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
@@ -5814,7 +5817,7 @@
         <v>367</v>
       </c>
       <c r="C359" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
@@ -5825,7 +5828,7 @@
         <v>361</v>
       </c>
       <c r="C360" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
@@ -5833,10 +5836,10 @@
         <v>321</v>
       </c>
       <c r="B361" t="s">
+        <v>484</v>
+      </c>
+      <c r="C361" t="s">
         <v>489</v>
-      </c>
-      <c r="C361" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
@@ -5844,10 +5847,10 @@
         <v>322</v>
       </c>
       <c r="B362" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C362" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
@@ -5858,7 +5861,7 @@
         <v>365</v>
       </c>
       <c r="C363" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
@@ -5869,7 +5872,7 @@
         <v>361</v>
       </c>
       <c r="C364" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
@@ -5880,7 +5883,7 @@
         <v>367</v>
       </c>
       <c r="C365" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
@@ -5891,7 +5894,7 @@
         <v>472</v>
       </c>
       <c r="C366" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
@@ -5902,7 +5905,7 @@
         <v>365</v>
       </c>
       <c r="C367" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
@@ -5913,7 +5916,7 @@
         <v>365</v>
       </c>
       <c r="C368" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
@@ -5924,7 +5927,7 @@
         <v>473</v>
       </c>
       <c r="C369" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
@@ -5932,10 +5935,10 @@
         <v>329</v>
       </c>
       <c r="B370" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C370" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
@@ -5946,7 +5949,7 @@
         <v>416</v>
       </c>
       <c r="C371" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
@@ -5965,10 +5968,10 @@
         <v>332</v>
       </c>
       <c r="B373" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C373" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
@@ -5976,7 +5979,7 @@
         <v>333</v>
       </c>
       <c r="B374" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C374" t="s">
         <v>478</v>
@@ -5990,7 +5993,7 @@
         <v>474</v>
       </c>
       <c r="C375" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
@@ -5998,10 +6001,10 @@
         <v>335</v>
       </c>
       <c r="B376" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C376" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
@@ -6012,7 +6015,7 @@
         <v>475</v>
       </c>
       <c r="C377" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
@@ -6023,7 +6026,7 @@
         <v>365</v>
       </c>
       <c r="C378" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
@@ -6034,7 +6037,7 @@
         <v>365</v>
       </c>
       <c r="C379" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
@@ -6042,10 +6045,10 @@
         <v>338</v>
       </c>
       <c r="B380" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C380" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
@@ -6056,7 +6059,7 @@
         <v>398</v>
       </c>
       <c r="C381" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
@@ -6067,7 +6070,7 @@
         <v>398</v>
       </c>
       <c r="C382" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
@@ -6078,7 +6081,7 @@
         <v>398</v>
       </c>
       <c r="C383" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
@@ -6089,7 +6092,7 @@
         <v>426</v>
       </c>
       <c r="C384" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
@@ -6097,10 +6100,10 @@
         <v>342</v>
       </c>
       <c r="B385" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C385" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
@@ -6111,7 +6114,7 @@
         <v>393</v>
       </c>
       <c r="C386" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
@@ -6122,7 +6125,7 @@
         <v>364</v>
       </c>
       <c r="C387" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
@@ -6133,7 +6136,7 @@
         <v>400</v>
       </c>
       <c r="C388" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
@@ -6152,10 +6155,10 @@
         <v>346</v>
       </c>
       <c r="B390" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C390" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
@@ -6166,7 +6169,7 @@
         <v>441</v>
       </c>
       <c r="C391" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
@@ -6177,7 +6180,7 @@
         <v>373</v>
       </c>
       <c r="C392" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
@@ -6188,7 +6191,7 @@
         <v>453</v>
       </c>
       <c r="C393" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
@@ -6199,7 +6202,7 @@
         <v>361</v>
       </c>
       <c r="C394" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
@@ -6218,10 +6221,10 @@
         <v>352</v>
       </c>
       <c r="B396" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C396" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
@@ -6232,7 +6235,7 @@
         <v>400</v>
       </c>
       <c r="C397" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
@@ -6240,10 +6243,10 @@
         <v>354</v>
       </c>
       <c r="B398" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C398" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
@@ -6251,10 +6254,10 @@
         <v>355</v>
       </c>
       <c r="B399" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C399" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
@@ -6265,7 +6268,7 @@
         <v>476</v>
       </c>
       <c r="C400" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
@@ -6273,7 +6276,7 @@
         <v>357</v>
       </c>
       <c r="B401" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C401" t="s">
         <v>478</v>
@@ -6287,7 +6290,7 @@
         <v>477</v>
       </c>
       <c r="C402" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
@@ -6298,7 +6301,7 @@
         <v>454</v>
       </c>
       <c r="C403" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/JCFD Fire Calls - Dashboard v1.xlsx
+++ b/JCFD Fire Calls - Dashboard v1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hbhklaw-my.sharepoint.com/personal/king_hbhklaw_com/Documents/Downloads/jcfd_streamlit_app/jcfd_streamlit_app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hbhklaw-my.sharepoint.com/personal/king_hbhklaw_com/Documents/Documents/Jordans Chapel VFD/jcfd-dashboard/jcfd_streamlit_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="12" documentId="8_{02908EFB-1241-4151-BB84-5E30A49FADCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7E0DC0A-EBC1-4266-844D-17FCD0C39535}"/>

--- a/JCFD Fire Calls - Dashboard v1.xlsx
+++ b/JCFD Fire Calls - Dashboard v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hbhklaw-my.sharepoint.com/personal/king_hbhklaw_com/Documents/Documents/Jordans Chapel VFD/jcfd-dashboard/jcfd_streamlit_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{02908EFB-1241-4151-BB84-5E30A49FADCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7E0DC0A-EBC1-4266-844D-17FCD0C39535}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{02908EFB-1241-4151-BB84-5E30A49FADCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E464F22-B8CA-40D8-ACD6-7C69E10438D9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="490">
   <si>
     <t>Date</t>
   </si>
@@ -1408,9 +1408,6 @@
     <t>Main St, Newton Grove (Family Dollar)</t>
   </si>
   <si>
-    <t>S US 13 Hwy &amp; Jordans Chapel Rd</t>
-  </si>
-  <si>
     <t>Dobbersville &amp; Slapout</t>
   </si>
   <si>
@@ -1484,9 +1481,6 @@
   </si>
   <si>
     <t>EMS</t>
-  </si>
-  <si>
-    <t>Investigation</t>
   </si>
   <si>
     <t>Investigate</t>
@@ -1574,6 +1568,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1887,10 +1885,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1901,7 +1899,7 @@
         <v>365</v>
       </c>
       <c r="C3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1909,10 +1907,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1923,7 +1921,7 @@
         <v>360</v>
       </c>
       <c r="C5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -1934,7 +1932,7 @@
         <v>361</v>
       </c>
       <c r="C6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -1945,7 +1943,7 @@
         <v>362</v>
       </c>
       <c r="C7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -1956,7 +1954,7 @@
         <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1964,10 +1962,10 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -1978,7 +1976,7 @@
         <v>363</v>
       </c>
       <c r="C10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -1989,7 +1987,7 @@
         <v>364</v>
       </c>
       <c r="C11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -2000,7 +1998,7 @@
         <v>364</v>
       </c>
       <c r="C12" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -2011,7 +2009,7 @@
         <v>365</v>
       </c>
       <c r="C13" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -2022,7 +2020,7 @@
         <v>365</v>
       </c>
       <c r="C14" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -2033,7 +2031,7 @@
         <v>366</v>
       </c>
       <c r="C15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -2044,7 +2042,7 @@
         <v>367</v>
       </c>
       <c r="C16" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -2052,10 +2050,10 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -2063,10 +2061,10 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C18" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -2077,7 +2075,7 @@
         <v>368</v>
       </c>
       <c r="C19" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -2088,7 +2086,7 @@
         <v>369</v>
       </c>
       <c r="C20" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -2099,7 +2097,7 @@
         <v>370</v>
       </c>
       <c r="C21" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -2110,7 +2108,7 @@
         <v>371</v>
       </c>
       <c r="C22" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -2121,7 +2119,7 @@
         <v>372</v>
       </c>
       <c r="C23" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -2132,7 +2130,7 @@
         <v>373</v>
       </c>
       <c r="C24" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -2143,7 +2141,7 @@
         <v>364</v>
       </c>
       <c r="C25" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -2151,10 +2149,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C26" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -2165,7 +2163,7 @@
         <v>360</v>
       </c>
       <c r="C27" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -2173,10 +2171,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C28" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -2184,10 +2182,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C29" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -2198,7 +2196,7 @@
         <v>374</v>
       </c>
       <c r="C30" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -2206,10 +2204,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C31" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -2217,10 +2215,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C32" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -2231,7 +2229,7 @@
         <v>375</v>
       </c>
       <c r="C33" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -2239,10 +2237,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C34" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -2253,7 +2251,7 @@
         <v>376</v>
       </c>
       <c r="C35" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -2264,7 +2262,7 @@
         <v>377</v>
       </c>
       <c r="C36" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -2272,10 +2270,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C37" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -2286,7 +2284,7 @@
         <v>365</v>
       </c>
       <c r="C38" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -2297,7 +2295,7 @@
         <v>364</v>
       </c>
       <c r="C39" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -2308,7 +2306,7 @@
         <v>378</v>
       </c>
       <c r="C40" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -2319,7 +2317,7 @@
         <v>379</v>
       </c>
       <c r="C41" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -2330,7 +2328,7 @@
         <v>379</v>
       </c>
       <c r="C42" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -2341,7 +2339,7 @@
         <v>365</v>
       </c>
       <c r="C43" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -2349,10 +2347,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C44" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -2360,10 +2358,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C45" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -2374,7 +2372,7 @@
         <v>365</v>
       </c>
       <c r="C46" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -2382,10 +2380,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C47" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -2393,10 +2391,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C48" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -2407,7 +2405,7 @@
         <v>380</v>
       </c>
       <c r="C49" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -2418,7 +2416,7 @@
         <v>377</v>
       </c>
       <c r="C50" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -2429,7 +2427,7 @@
         <v>381</v>
       </c>
       <c r="C51" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -2440,7 +2438,7 @@
         <v>382</v>
       </c>
       <c r="C52" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -2451,7 +2449,7 @@
         <v>360</v>
       </c>
       <c r="C53" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -2462,7 +2460,7 @@
         <v>383</v>
       </c>
       <c r="C54" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -2473,7 +2471,7 @@
         <v>378</v>
       </c>
       <c r="C55" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -2484,7 +2482,7 @@
         <v>364</v>
       </c>
       <c r="C56" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -2492,10 +2490,10 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C57" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -2506,7 +2504,7 @@
         <v>384</v>
       </c>
       <c r="C58" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -2517,7 +2515,7 @@
         <v>366</v>
       </c>
       <c r="C59" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -2525,10 +2523,10 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C60" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -2539,7 +2537,7 @@
         <v>385</v>
       </c>
       <c r="C61" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -2550,7 +2548,7 @@
         <v>378</v>
       </c>
       <c r="C62" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -2558,10 +2556,10 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C63" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -2572,7 +2570,7 @@
         <v>386</v>
       </c>
       <c r="C64" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -2580,10 +2578,10 @@
         <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C65" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -2594,7 +2592,7 @@
         <v>387</v>
       </c>
       <c r="C66" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -2602,10 +2600,10 @@
         <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C67" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
@@ -2616,7 +2614,7 @@
         <v>388</v>
       </c>
       <c r="C68" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -2627,7 +2625,7 @@
         <v>368</v>
       </c>
       <c r="C69" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -2638,7 +2636,7 @@
         <v>386</v>
       </c>
       <c r="C70" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -2649,7 +2647,7 @@
         <v>359</v>
       </c>
       <c r="C71" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -2657,10 +2655,10 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C72" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -2668,10 +2666,10 @@
         <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C73" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
@@ -2682,7 +2680,7 @@
         <v>389</v>
       </c>
       <c r="C74" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
@@ -2690,10 +2688,10 @@
         <v>69</v>
       </c>
       <c r="B75" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C75" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
@@ -2701,10 +2699,10 @@
         <v>70</v>
       </c>
       <c r="B76" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C76" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
@@ -2715,7 +2713,7 @@
         <v>364</v>
       </c>
       <c r="C77" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
@@ -2726,7 +2724,7 @@
         <v>364</v>
       </c>
       <c r="C78" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -2737,7 +2735,7 @@
         <v>390</v>
       </c>
       <c r="C79" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
@@ -2748,7 +2746,7 @@
         <v>367</v>
       </c>
       <c r="C80" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
@@ -2756,10 +2754,10 @@
         <v>75</v>
       </c>
       <c r="B81" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C81" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
@@ -2770,7 +2768,7 @@
         <v>391</v>
       </c>
       <c r="C82" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
@@ -2781,7 +2779,7 @@
         <v>392</v>
       </c>
       <c r="C83" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
@@ -2792,7 +2790,7 @@
         <v>406</v>
       </c>
       <c r="C84" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -2803,7 +2801,7 @@
         <v>360</v>
       </c>
       <c r="C85" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
@@ -2814,7 +2812,7 @@
         <v>393</v>
       </c>
       <c r="C86" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
@@ -2825,7 +2823,7 @@
         <v>394</v>
       </c>
       <c r="C87" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
@@ -2833,10 +2831,10 @@
         <v>81</v>
       </c>
       <c r="B88" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C88" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
@@ -2847,7 +2845,7 @@
         <v>394</v>
       </c>
       <c r="C89" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
@@ -2858,7 +2856,7 @@
         <v>395</v>
       </c>
       <c r="C90" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
@@ -2866,10 +2864,10 @@
         <v>83</v>
       </c>
       <c r="B91" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C91" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
@@ -2880,7 +2878,7 @@
         <v>396</v>
       </c>
       <c r="C92" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
@@ -2888,10 +2886,10 @@
         <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C93" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
@@ -2899,10 +2897,10 @@
         <v>86</v>
       </c>
       <c r="B94" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C94" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
@@ -2913,7 +2911,7 @@
         <v>360</v>
       </c>
       <c r="C95" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
@@ -2924,7 +2922,7 @@
         <v>379</v>
       </c>
       <c r="C96" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
@@ -2935,7 +2933,7 @@
         <v>365</v>
       </c>
       <c r="C97" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
@@ -2946,7 +2944,7 @@
         <v>360</v>
       </c>
       <c r="C98" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
@@ -2954,10 +2952,10 @@
         <v>90</v>
       </c>
       <c r="B99" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C99" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
@@ -2968,7 +2966,7 @@
         <v>368</v>
       </c>
       <c r="C100" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
@@ -2979,7 +2977,7 @@
         <v>367</v>
       </c>
       <c r="C101" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
@@ -2990,7 +2988,7 @@
         <v>397</v>
       </c>
       <c r="C102" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
@@ -3001,7 +2999,7 @@
         <v>383</v>
       </c>
       <c r="C103" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
@@ -3012,7 +3010,7 @@
         <v>398</v>
       </c>
       <c r="C104" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
@@ -3023,7 +3021,7 @@
         <v>399</v>
       </c>
       <c r="C105" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
@@ -3031,10 +3029,10 @@
         <v>97</v>
       </c>
       <c r="B106" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C106" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
@@ -3045,7 +3043,7 @@
         <v>400</v>
       </c>
       <c r="C107" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
@@ -3056,7 +3054,7 @@
         <v>401</v>
       </c>
       <c r="C108" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
@@ -3067,7 +3065,7 @@
         <v>402</v>
       </c>
       <c r="C109" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
@@ -3078,7 +3076,7 @@
         <v>403</v>
       </c>
       <c r="C110" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
@@ -3089,7 +3087,7 @@
         <v>404</v>
       </c>
       <c r="C111" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
@@ -3100,7 +3098,7 @@
         <v>404</v>
       </c>
       <c r="C112" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
@@ -3111,7 +3109,7 @@
         <v>405</v>
       </c>
       <c r="C113" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
@@ -3119,10 +3117,10 @@
         <v>104</v>
       </c>
       <c r="B114" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C114" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
@@ -3133,7 +3131,7 @@
         <v>403</v>
       </c>
       <c r="C115" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
@@ -3144,7 +3142,7 @@
         <v>382</v>
       </c>
       <c r="C116" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
@@ -3155,7 +3153,7 @@
         <v>406</v>
       </c>
       <c r="C117" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -3166,7 +3164,7 @@
         <v>364</v>
       </c>
       <c r="C118" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -3177,7 +3175,7 @@
         <v>361</v>
       </c>
       <c r="C119" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
@@ -3188,7 +3186,7 @@
         <v>400</v>
       </c>
       <c r="C120" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -3199,7 +3197,7 @@
         <v>365</v>
       </c>
       <c r="C121" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -3207,10 +3205,10 @@
         <v>111</v>
       </c>
       <c r="B122" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C122" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
@@ -3221,7 +3219,7 @@
         <v>407</v>
       </c>
       <c r="C123" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
@@ -3229,10 +3227,10 @@
         <v>113</v>
       </c>
       <c r="B124" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C124" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
@@ -3243,7 +3241,7 @@
         <v>398</v>
       </c>
       <c r="C125" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -3254,7 +3252,7 @@
         <v>408</v>
       </c>
       <c r="C126" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -3265,7 +3263,7 @@
         <v>368</v>
       </c>
       <c r="C127" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
@@ -3276,7 +3274,7 @@
         <v>367</v>
       </c>
       <c r="C128" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
@@ -3284,10 +3282,10 @@
         <v>117</v>
       </c>
       <c r="B129" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C129" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
@@ -3295,10 +3293,10 @@
         <v>118</v>
       </c>
       <c r="B130" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C130" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
@@ -3309,7 +3307,7 @@
         <v>380</v>
       </c>
       <c r="C131" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
@@ -3320,7 +3318,7 @@
         <v>409</v>
       </c>
       <c r="C132" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
@@ -3328,10 +3326,10 @@
         <v>121</v>
       </c>
       <c r="B133" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C133" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
@@ -3342,7 +3340,7 @@
         <v>410</v>
       </c>
       <c r="C134" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
@@ -3350,10 +3348,10 @@
         <v>123</v>
       </c>
       <c r="B135" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C135" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
@@ -3364,7 +3362,7 @@
         <v>411</v>
       </c>
       <c r="C136" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -3375,7 +3373,7 @@
         <v>403</v>
       </c>
       <c r="C137" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -3386,7 +3384,7 @@
         <v>360</v>
       </c>
       <c r="C138" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
@@ -3394,10 +3392,10 @@
         <v>127</v>
       </c>
       <c r="B139" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C139" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -3408,7 +3406,7 @@
         <v>385</v>
       </c>
       <c r="C140" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -3419,7 +3417,7 @@
         <v>410</v>
       </c>
       <c r="C141" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -3430,7 +3428,7 @@
         <v>361</v>
       </c>
       <c r="C142" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -3441,7 +3439,7 @@
         <v>368</v>
       </c>
       <c r="C143" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -3452,7 +3450,7 @@
         <v>403</v>
       </c>
       <c r="C144" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -3460,10 +3458,10 @@
         <v>133</v>
       </c>
       <c r="B145" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C145" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
@@ -3474,7 +3472,7 @@
         <v>360</v>
       </c>
       <c r="C146" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
@@ -3485,7 +3483,7 @@
         <v>412</v>
       </c>
       <c r="C147" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -3493,10 +3491,10 @@
         <v>136</v>
       </c>
       <c r="B148" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C148" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -3507,7 +3505,7 @@
         <v>382</v>
       </c>
       <c r="C149" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -3518,7 +3516,7 @@
         <v>413</v>
       </c>
       <c r="C150" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -3529,7 +3527,7 @@
         <v>414</v>
       </c>
       <c r="C151" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -3540,7 +3538,7 @@
         <v>415</v>
       </c>
       <c r="C152" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -3551,7 +3549,7 @@
         <v>416</v>
       </c>
       <c r="C153" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -3562,7 +3560,7 @@
         <v>385</v>
       </c>
       <c r="C154" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -3573,7 +3571,7 @@
         <v>417</v>
       </c>
       <c r="C155" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -3584,7 +3582,7 @@
         <v>398</v>
       </c>
       <c r="C156" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -3595,7 +3593,7 @@
         <v>418</v>
       </c>
       <c r="C157" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -3606,7 +3604,7 @@
         <v>406</v>
       </c>
       <c r="C158" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -3614,10 +3612,10 @@
         <v>146</v>
       </c>
       <c r="B159" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C159" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -3625,10 +3623,10 @@
         <v>147</v>
       </c>
       <c r="B160" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C160" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -3639,7 +3637,7 @@
         <v>419</v>
       </c>
       <c r="C161" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -3647,10 +3645,10 @@
         <v>149</v>
       </c>
       <c r="B162" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C162" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -3661,7 +3659,7 @@
         <v>420</v>
       </c>
       <c r="C163" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -3672,7 +3670,7 @@
         <v>421</v>
       </c>
       <c r="C164" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -3683,7 +3681,7 @@
         <v>405</v>
       </c>
       <c r="C165" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -3694,7 +3692,7 @@
         <v>422</v>
       </c>
       <c r="C166" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -3705,7 +3703,7 @@
         <v>423</v>
       </c>
       <c r="C167" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
@@ -3716,7 +3714,7 @@
         <v>379</v>
       </c>
       <c r="C168" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
@@ -3727,7 +3725,7 @@
         <v>379</v>
       </c>
       <c r="C169" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
@@ -3738,7 +3736,7 @@
         <v>396</v>
       </c>
       <c r="C170" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
@@ -3749,7 +3747,7 @@
         <v>422</v>
       </c>
       <c r="C171" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
@@ -3760,7 +3758,7 @@
         <v>424</v>
       </c>
       <c r="C172" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -3771,7 +3769,7 @@
         <v>378</v>
       </c>
       <c r="C173" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
@@ -3779,10 +3777,10 @@
         <v>159</v>
       </c>
       <c r="B174" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C174" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
@@ -3793,7 +3791,7 @@
         <v>367</v>
       </c>
       <c r="C175" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
@@ -3804,7 +3802,7 @@
         <v>425</v>
       </c>
       <c r="C176" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
@@ -3815,7 +3813,7 @@
         <v>365</v>
       </c>
       <c r="C177" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
@@ -3826,7 +3824,7 @@
         <v>421</v>
       </c>
       <c r="C178" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
@@ -3837,7 +3835,7 @@
         <v>426</v>
       </c>
       <c r="C179" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
@@ -3845,10 +3843,10 @@
         <v>164</v>
       </c>
       <c r="B180" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C180" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
@@ -3859,7 +3857,7 @@
         <v>427</v>
       </c>
       <c r="C181" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
@@ -3870,7 +3868,7 @@
         <v>428</v>
       </c>
       <c r="C182" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
@@ -3881,7 +3879,7 @@
         <v>429</v>
       </c>
       <c r="C183" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
@@ -3892,7 +3890,7 @@
         <v>430</v>
       </c>
       <c r="C184" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
@@ -3903,7 +3901,7 @@
         <v>375</v>
       </c>
       <c r="C185" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
@@ -3914,7 +3912,7 @@
         <v>365</v>
       </c>
       <c r="C186" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
@@ -3925,7 +3923,7 @@
         <v>431</v>
       </c>
       <c r="C187" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
@@ -3936,7 +3934,7 @@
         <v>428</v>
       </c>
       <c r="C188" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
@@ -3947,7 +3945,7 @@
         <v>432</v>
       </c>
       <c r="C189" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
@@ -3958,7 +3956,7 @@
         <v>386</v>
       </c>
       <c r="C190" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
@@ -3966,10 +3964,10 @@
         <v>172</v>
       </c>
       <c r="B191" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C191" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -3980,7 +3978,7 @@
         <v>361</v>
       </c>
       <c r="C192" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
@@ -3991,7 +3989,7 @@
         <v>365</v>
       </c>
       <c r="C193" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
@@ -4002,7 +4000,7 @@
         <v>409</v>
       </c>
       <c r="C194" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
@@ -4013,7 +4011,7 @@
         <v>433</v>
       </c>
       <c r="C195" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
@@ -4024,7 +4022,7 @@
         <v>368</v>
       </c>
       <c r="C196" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
@@ -4035,7 +4033,7 @@
         <v>426</v>
       </c>
       <c r="C197" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
@@ -4046,7 +4044,7 @@
         <v>365</v>
       </c>
       <c r="C198" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
@@ -4057,7 +4055,7 @@
         <v>434</v>
       </c>
       <c r="C199" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
@@ -4065,10 +4063,10 @@
         <v>177</v>
       </c>
       <c r="B200" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C200" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
@@ -4079,7 +4077,7 @@
         <v>368</v>
       </c>
       <c r="C201" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
@@ -4090,7 +4088,7 @@
         <v>368</v>
       </c>
       <c r="C202" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
@@ -4101,7 +4099,7 @@
         <v>360</v>
       </c>
       <c r="C203" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
@@ -4112,7 +4110,7 @@
         <v>435</v>
       </c>
       <c r="C204" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -4123,7 +4121,7 @@
         <v>426</v>
       </c>
       <c r="C205" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
@@ -4131,10 +4129,10 @@
         <v>182</v>
       </c>
       <c r="B206" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C206" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
@@ -4142,10 +4140,10 @@
         <v>182</v>
       </c>
       <c r="B207" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C207" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
@@ -4153,10 +4151,10 @@
         <v>183</v>
       </c>
       <c r="B208" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C208" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
@@ -4164,10 +4162,10 @@
         <v>184</v>
       </c>
       <c r="B209" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C209" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
@@ -4175,10 +4173,10 @@
         <v>185</v>
       </c>
       <c r="B210" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C210" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
@@ -4186,10 +4184,10 @@
         <v>186</v>
       </c>
       <c r="B211" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C211" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
@@ -4197,10 +4195,10 @@
         <v>187</v>
       </c>
       <c r="B212" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C212" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
@@ -4211,7 +4209,7 @@
         <v>361</v>
       </c>
       <c r="C213" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
@@ -4219,10 +4217,10 @@
         <v>189</v>
       </c>
       <c r="B214" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C214" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
@@ -4230,10 +4228,10 @@
         <v>190</v>
       </c>
       <c r="B215" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C215" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
@@ -4241,10 +4239,10 @@
         <v>191</v>
       </c>
       <c r="B216" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C216" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
@@ -4252,10 +4250,10 @@
         <v>191</v>
       </c>
       <c r="B217" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C217" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
@@ -4263,10 +4261,10 @@
         <v>191</v>
       </c>
       <c r="B218" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C218" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
@@ -4277,7 +4275,7 @@
         <v>361</v>
       </c>
       <c r="C219" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
@@ -4288,7 +4286,7 @@
         <v>361</v>
       </c>
       <c r="C220" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
@@ -4299,7 +4297,7 @@
         <v>398</v>
       </c>
       <c r="C221" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
@@ -4310,7 +4308,7 @@
         <v>436</v>
       </c>
       <c r="C222" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
@@ -4321,7 +4319,7 @@
         <v>437</v>
       </c>
       <c r="C223" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
@@ -4332,7 +4330,7 @@
         <v>393</v>
       </c>
       <c r="C224" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
@@ -4343,7 +4341,7 @@
         <v>365</v>
       </c>
       <c r="C225" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
@@ -4354,7 +4352,7 @@
         <v>365</v>
       </c>
       <c r="C226" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
@@ -4365,7 +4363,7 @@
         <v>438</v>
       </c>
       <c r="C227" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
@@ -4376,7 +4374,7 @@
         <v>426</v>
       </c>
       <c r="C228" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
@@ -4387,7 +4385,7 @@
         <v>393</v>
       </c>
       <c r="C229" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
@@ -4398,7 +4396,7 @@
         <v>365</v>
       </c>
       <c r="C230" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
@@ -4406,10 +4404,10 @@
         <v>203</v>
       </c>
       <c r="B231" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C231" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
@@ -4420,7 +4418,7 @@
         <v>426</v>
       </c>
       <c r="C232" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
@@ -4431,7 +4429,7 @@
         <v>365</v>
       </c>
       <c r="C233" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
@@ -4442,7 +4440,7 @@
         <v>426</v>
       </c>
       <c r="C234" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
@@ -4450,10 +4448,10 @@
         <v>207</v>
       </c>
       <c r="B235" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C235" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
@@ -4464,7 +4462,7 @@
         <v>373</v>
       </c>
       <c r="C236" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
@@ -4475,7 +4473,7 @@
         <v>382</v>
       </c>
       <c r="C237" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
@@ -4486,7 +4484,7 @@
         <v>426</v>
       </c>
       <c r="C238" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
@@ -4497,7 +4495,7 @@
         <v>365</v>
       </c>
       <c r="C239" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
@@ -4505,10 +4503,10 @@
         <v>212</v>
       </c>
       <c r="B240" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C240" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
@@ -4519,7 +4517,7 @@
         <v>426</v>
       </c>
       <c r="C241" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
@@ -4530,7 +4528,7 @@
         <v>426</v>
       </c>
       <c r="C242" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
@@ -4541,7 +4539,7 @@
         <v>426</v>
       </c>
       <c r="C243" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
@@ -4552,7 +4550,7 @@
         <v>426</v>
       </c>
       <c r="C244" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
@@ -4563,7 +4561,7 @@
         <v>426</v>
       </c>
       <c r="C245" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
@@ -4574,7 +4572,7 @@
         <v>361</v>
       </c>
       <c r="C246" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
@@ -4582,10 +4580,10 @@
         <v>219</v>
       </c>
       <c r="B247" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C247" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
@@ -4596,7 +4594,7 @@
         <v>439</v>
       </c>
       <c r="C248" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
@@ -4607,7 +4605,7 @@
         <v>426</v>
       </c>
       <c r="C249" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
@@ -4618,7 +4616,7 @@
         <v>365</v>
       </c>
       <c r="C250" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
@@ -4629,7 +4627,7 @@
         <v>426</v>
       </c>
       <c r="C251" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
@@ -4640,7 +4638,7 @@
         <v>440</v>
       </c>
       <c r="C252" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
@@ -4651,7 +4649,7 @@
         <v>379</v>
       </c>
       <c r="C253" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
@@ -4662,7 +4660,7 @@
         <v>426</v>
       </c>
       <c r="C254" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
@@ -4673,7 +4671,7 @@
         <v>367</v>
       </c>
       <c r="C255" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
@@ -4684,7 +4682,7 @@
         <v>365</v>
       </c>
       <c r="C256" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
@@ -4695,7 +4693,7 @@
         <v>441</v>
       </c>
       <c r="C257" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
@@ -4706,7 +4704,7 @@
         <v>442</v>
       </c>
       <c r="C258" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
@@ -4717,7 +4715,7 @@
         <v>426</v>
       </c>
       <c r="C259" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
@@ -4728,7 +4726,7 @@
         <v>398</v>
       </c>
       <c r="C260" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
@@ -4739,7 +4737,7 @@
         <v>443</v>
       </c>
       <c r="C261" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
@@ -4750,7 +4748,7 @@
         <v>380</v>
       </c>
       <c r="C262" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
@@ -4761,7 +4759,7 @@
         <v>400</v>
       </c>
       <c r="C263" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
@@ -4772,7 +4770,7 @@
         <v>426</v>
       </c>
       <c r="C264" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
@@ -4783,7 +4781,7 @@
         <v>361</v>
       </c>
       <c r="C265" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
@@ -4794,7 +4792,7 @@
         <v>428</v>
       </c>
       <c r="C266" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
@@ -4805,7 +4803,7 @@
         <v>426</v>
       </c>
       <c r="C267" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
@@ -4816,7 +4814,7 @@
         <v>426</v>
       </c>
       <c r="C268" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
@@ -4824,10 +4822,10 @@
         <v>240</v>
       </c>
       <c r="B269" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C269" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
@@ -4838,7 +4836,7 @@
         <v>366</v>
       </c>
       <c r="C270" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
@@ -4849,7 +4847,7 @@
         <v>382</v>
       </c>
       <c r="C271" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
@@ -4860,7 +4858,7 @@
         <v>444</v>
       </c>
       <c r="C272" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
@@ -4868,10 +4866,10 @@
         <v>243</v>
       </c>
       <c r="B273" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C273" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
@@ -4882,7 +4880,7 @@
         <v>426</v>
       </c>
       <c r="C274" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
@@ -4893,7 +4891,7 @@
         <v>445</v>
       </c>
       <c r="C275" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
@@ -4904,7 +4902,7 @@
         <v>446</v>
       </c>
       <c r="C276" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
@@ -4915,7 +4913,7 @@
         <v>447</v>
       </c>
       <c r="C277" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
@@ -4923,10 +4921,10 @@
         <v>246</v>
       </c>
       <c r="B278" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C278" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
@@ -4937,7 +4935,7 @@
         <v>361</v>
       </c>
       <c r="C279" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
@@ -4945,10 +4943,10 @@
         <v>248</v>
       </c>
       <c r="B280" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C280" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
@@ -4959,7 +4957,7 @@
         <v>441</v>
       </c>
       <c r="C281" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
@@ -4970,7 +4968,7 @@
         <v>441</v>
       </c>
       <c r="C282" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
@@ -4981,7 +4979,7 @@
         <v>365</v>
       </c>
       <c r="C283" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
@@ -4992,7 +4990,7 @@
         <v>448</v>
       </c>
       <c r="C284" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
@@ -5000,10 +4998,10 @@
         <v>253</v>
       </c>
       <c r="B285" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C285" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
@@ -5014,7 +5012,7 @@
         <v>449</v>
       </c>
       <c r="C286" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
@@ -5025,7 +5023,7 @@
         <v>382</v>
       </c>
       <c r="C287" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
@@ -5036,7 +5034,7 @@
         <v>450</v>
       </c>
       <c r="C288" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
@@ -5047,7 +5045,7 @@
         <v>451</v>
       </c>
       <c r="C289" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
@@ -5058,7 +5056,7 @@
         <v>452</v>
       </c>
       <c r="C290" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
@@ -5069,7 +5067,7 @@
         <v>426</v>
       </c>
       <c r="C291" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
@@ -5080,7 +5078,7 @@
         <v>379</v>
       </c>
       <c r="C292" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
@@ -5091,7 +5089,7 @@
         <v>405</v>
       </c>
       <c r="C293" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
@@ -5102,7 +5100,7 @@
         <v>453</v>
       </c>
       <c r="C294" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
@@ -5113,7 +5111,7 @@
         <v>454</v>
       </c>
       <c r="C295" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
@@ -5124,7 +5122,7 @@
         <v>455</v>
       </c>
       <c r="C296" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
@@ -5135,7 +5133,7 @@
         <v>426</v>
       </c>
       <c r="C297" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
@@ -5143,10 +5141,10 @@
         <v>263</v>
       </c>
       <c r="B298" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C298" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
@@ -5157,7 +5155,7 @@
         <v>438</v>
       </c>
       <c r="C299" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
@@ -5168,7 +5166,7 @@
         <v>450</v>
       </c>
       <c r="C300" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
@@ -5176,10 +5174,10 @@
         <v>266</v>
       </c>
       <c r="B301" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C301" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
@@ -5190,7 +5188,7 @@
         <v>428</v>
       </c>
       <c r="C302" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
@@ -5201,7 +5199,7 @@
         <v>456</v>
       </c>
       <c r="C303" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
@@ -5212,7 +5210,7 @@
         <v>398</v>
       </c>
       <c r="C304" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
@@ -5223,7 +5221,7 @@
         <v>457</v>
       </c>
       <c r="C305" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
@@ -5234,7 +5232,7 @@
         <v>365</v>
       </c>
       <c r="C306" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
@@ -5245,7 +5243,7 @@
         <v>458</v>
       </c>
       <c r="C307" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
@@ -5256,7 +5254,7 @@
         <v>459</v>
       </c>
       <c r="C308" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
@@ -5267,7 +5265,7 @@
         <v>426</v>
       </c>
       <c r="C309" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
@@ -5278,7 +5276,7 @@
         <v>361</v>
       </c>
       <c r="C310" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
@@ -5286,10 +5284,10 @@
         <v>276</v>
       </c>
       <c r="B311" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C311" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
@@ -5300,7 +5298,7 @@
         <v>382</v>
       </c>
       <c r="C312" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
@@ -5311,7 +5309,7 @@
         <v>396</v>
       </c>
       <c r="C313" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
@@ -5322,7 +5320,7 @@
         <v>460</v>
       </c>
       <c r="C314" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
@@ -5330,10 +5328,10 @@
         <v>279</v>
       </c>
       <c r="B315" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C315" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.35">
@@ -5344,7 +5342,7 @@
         <v>461</v>
       </c>
       <c r="C316" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.35">
@@ -5352,10 +5350,10 @@
         <v>281</v>
       </c>
       <c r="B317" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C317" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.35">
@@ -5363,10 +5361,10 @@
         <v>282</v>
       </c>
       <c r="B318" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C318" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.35">
@@ -5377,7 +5375,7 @@
         <v>365</v>
       </c>
       <c r="C319" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.35">
@@ -5388,7 +5386,7 @@
         <v>365</v>
       </c>
       <c r="C320" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.35">
@@ -5399,7 +5397,7 @@
         <v>361</v>
       </c>
       <c r="C321" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.35">
@@ -5407,10 +5405,10 @@
         <v>286</v>
       </c>
       <c r="B322" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="C322" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.35">
@@ -5418,10 +5416,10 @@
         <v>287</v>
       </c>
       <c r="B323" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C323" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.35">
@@ -5432,7 +5430,7 @@
         <v>426</v>
       </c>
       <c r="C324" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.35">
@@ -5440,10 +5438,10 @@
         <v>289</v>
       </c>
       <c r="B325" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C325" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.35">
@@ -5454,7 +5452,7 @@
         <v>379</v>
       </c>
       <c r="C326" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.35">
@@ -5465,7 +5463,7 @@
         <v>385</v>
       </c>
       <c r="C327" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.35">
@@ -5473,10 +5471,10 @@
         <v>292</v>
       </c>
       <c r="B328" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C328" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.35">
@@ -5484,10 +5482,10 @@
         <v>293</v>
       </c>
       <c r="B329" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C329" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.35">
@@ -5495,10 +5493,10 @@
         <v>294</v>
       </c>
       <c r="B330" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C330" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.35">
@@ -5506,10 +5504,10 @@
         <v>295</v>
       </c>
       <c r="B331" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C331" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.35">
@@ -5520,7 +5518,7 @@
         <v>380</v>
       </c>
       <c r="C332" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.35">
@@ -5531,7 +5529,7 @@
         <v>398</v>
       </c>
       <c r="C333" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.35">
@@ -5542,7 +5540,7 @@
         <v>361</v>
       </c>
       <c r="C334" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.35">
@@ -5553,7 +5551,7 @@
         <v>426</v>
       </c>
       <c r="C335" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.35">
@@ -5564,7 +5562,7 @@
         <v>363</v>
       </c>
       <c r="C336" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.35">
@@ -5575,7 +5573,7 @@
         <v>365</v>
       </c>
       <c r="C337" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.35">
@@ -5586,7 +5584,7 @@
         <v>373</v>
       </c>
       <c r="C338" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.35">
@@ -5594,10 +5592,10 @@
         <v>302</v>
       </c>
       <c r="B339" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C339" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.35">
@@ -5608,7 +5606,7 @@
         <v>426</v>
       </c>
       <c r="C340" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.35">
@@ -5616,10 +5614,10 @@
         <v>304</v>
       </c>
       <c r="B341" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C341" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.35">
@@ -5627,10 +5625,10 @@
         <v>305</v>
       </c>
       <c r="B342" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C342" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.35">
@@ -5641,7 +5639,7 @@
         <v>450</v>
       </c>
       <c r="C343" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.35">
@@ -5649,10 +5647,10 @@
         <v>307</v>
       </c>
       <c r="B344" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C344" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.35">
@@ -5660,10 +5658,10 @@
         <v>308</v>
       </c>
       <c r="B345" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C345" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.35">
@@ -5671,10 +5669,10 @@
         <v>309</v>
       </c>
       <c r="B346" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C346" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.35">
@@ -5685,7 +5683,7 @@
         <v>368</v>
       </c>
       <c r="C347" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.35">
@@ -5696,7 +5694,7 @@
         <v>365</v>
       </c>
       <c r="C348" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.35">
@@ -5704,10 +5702,10 @@
         <v>311</v>
       </c>
       <c r="B349" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C349" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.35">
@@ -5718,7 +5716,7 @@
         <v>426</v>
       </c>
       <c r="C350" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.35">
@@ -5729,7 +5727,7 @@
         <v>416</v>
       </c>
       <c r="C351" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.35">
@@ -5740,7 +5738,7 @@
         <v>365</v>
       </c>
       <c r="C352" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.35">
@@ -5751,7 +5749,7 @@
         <v>380</v>
       </c>
       <c r="C353" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.35">
@@ -5759,10 +5757,10 @@
         <v>315</v>
       </c>
       <c r="B354" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C354" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.35">
@@ -5773,7 +5771,7 @@
         <v>448</v>
       </c>
       <c r="C355" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.35">
@@ -5784,7 +5782,7 @@
         <v>367</v>
       </c>
       <c r="C356" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.35">
@@ -5792,10 +5790,10 @@
         <v>317</v>
       </c>
       <c r="B357" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C357" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.35">
@@ -5806,7 +5804,7 @@
         <v>360</v>
       </c>
       <c r="C358" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.35">
@@ -5817,7 +5815,7 @@
         <v>367</v>
       </c>
       <c r="C359" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.35">
@@ -5828,7 +5826,7 @@
         <v>361</v>
       </c>
       <c r="C360" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.35">
@@ -5836,10 +5834,10 @@
         <v>321</v>
       </c>
       <c r="B361" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C361" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.35">
@@ -5847,10 +5845,10 @@
         <v>322</v>
       </c>
       <c r="B362" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C362" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.35">
@@ -5861,7 +5859,7 @@
         <v>365</v>
       </c>
       <c r="C363" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.35">
@@ -5872,7 +5870,7 @@
         <v>361</v>
       </c>
       <c r="C364" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.35">
@@ -5883,7 +5881,7 @@
         <v>367</v>
       </c>
       <c r="C365" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.35">
@@ -5891,10 +5889,10 @@
         <v>326</v>
       </c>
       <c r="B366" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C366" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.35">
@@ -5905,7 +5903,7 @@
         <v>365</v>
       </c>
       <c r="C367" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.35">
@@ -5916,7 +5914,7 @@
         <v>365</v>
       </c>
       <c r="C368" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.35">
@@ -5924,10 +5922,10 @@
         <v>328</v>
       </c>
       <c r="B369" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C369" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.35">
@@ -5935,10 +5933,10 @@
         <v>329</v>
       </c>
       <c r="B370" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C370" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.35">
@@ -5949,7 +5947,7 @@
         <v>416</v>
       </c>
       <c r="C371" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.35">
@@ -5960,7 +5958,7 @@
         <v>426</v>
       </c>
       <c r="C372" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.35">
@@ -5968,10 +5966,10 @@
         <v>332</v>
       </c>
       <c r="B373" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C373" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.35">
@@ -5979,10 +5977,10 @@
         <v>333</v>
       </c>
       <c r="B374" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C374" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.35">
@@ -5990,10 +5988,10 @@
         <v>334</v>
       </c>
       <c r="B375" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C375" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.35">
@@ -6001,10 +5999,10 @@
         <v>335</v>
       </c>
       <c r="B376" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C376" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.35">
@@ -6012,10 +6010,10 @@
         <v>336</v>
       </c>
       <c r="B377" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C377" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.35">
@@ -6026,7 +6024,7 @@
         <v>365</v>
       </c>
       <c r="C378" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.35">
@@ -6037,7 +6035,7 @@
         <v>365</v>
       </c>
       <c r="C379" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.35">
@@ -6045,10 +6043,10 @@
         <v>338</v>
       </c>
       <c r="B380" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C380" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.35">
@@ -6059,7 +6057,7 @@
         <v>398</v>
       </c>
       <c r="C381" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.35">
@@ -6070,7 +6068,7 @@
         <v>398</v>
       </c>
       <c r="C382" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.35">
@@ -6081,7 +6079,7 @@
         <v>398</v>
       </c>
       <c r="C383" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.35">
@@ -6092,7 +6090,7 @@
         <v>426</v>
       </c>
       <c r="C384" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.35">
@@ -6100,10 +6098,10 @@
         <v>342</v>
       </c>
       <c r="B385" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C385" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.35">
@@ -6114,7 +6112,7 @@
         <v>393</v>
       </c>
       <c r="C386" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.35">
@@ -6125,7 +6123,7 @@
         <v>364</v>
       </c>
       <c r="C387" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.35">
@@ -6136,7 +6134,7 @@
         <v>400</v>
       </c>
       <c r="C388" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.35">
@@ -6147,7 +6145,7 @@
         <v>426</v>
       </c>
       <c r="C389" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.35">
@@ -6155,10 +6153,10 @@
         <v>346</v>
       </c>
       <c r="B390" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C390" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.35">
@@ -6169,7 +6167,7 @@
         <v>441</v>
       </c>
       <c r="C391" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.35">
@@ -6180,7 +6178,7 @@
         <v>373</v>
       </c>
       <c r="C392" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.35">
@@ -6191,7 +6189,7 @@
         <v>453</v>
       </c>
       <c r="C393" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.35">
@@ -6202,7 +6200,7 @@
         <v>361</v>
       </c>
       <c r="C394" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.35">
@@ -6213,7 +6211,7 @@
         <v>365</v>
       </c>
       <c r="C395" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.35">
@@ -6221,10 +6219,10 @@
         <v>352</v>
       </c>
       <c r="B396" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C396" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.35">
@@ -6235,7 +6233,7 @@
         <v>400</v>
       </c>
       <c r="C397" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.35">
@@ -6243,10 +6241,10 @@
         <v>354</v>
       </c>
       <c r="B398" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C398" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.35">
@@ -6254,10 +6252,10 @@
         <v>355</v>
       </c>
       <c r="B399" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C399" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.35">
@@ -6265,10 +6263,10 @@
         <v>356</v>
       </c>
       <c r="B400" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C400" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.35">
@@ -6276,10 +6274,10 @@
         <v>357</v>
       </c>
       <c r="B401" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C401" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.35">
@@ -6287,10 +6285,10 @@
         <v>358</v>
       </c>
       <c r="B402" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C402" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.35">
@@ -6301,7 +6299,7 @@
         <v>454</v>
       </c>
       <c r="C403" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/JCFD Fire Calls - Dashboard v1.xlsx
+++ b/JCFD Fire Calls - Dashboard v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hbhklaw-my.sharepoint.com/personal/king_hbhklaw_com/Documents/Documents/Jordans Chapel VFD/jcfd-dashboard/jcfd_streamlit_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{02908EFB-1241-4151-BB84-5E30A49FADCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E464F22-B8CA-40D8-ACD6-7C69E10438D9}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{02908EFB-1241-4151-BB84-5E30A49FADCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C2B0454-4460-47C6-9ECF-07ECF188BBE8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="493">
   <si>
     <t>Date</t>
   </si>
@@ -1490,12 +1490,24 @@
   </si>
   <si>
     <t>Mutual Aid - Unspecified</t>
+  </si>
+  <si>
+    <t>Crows Foot Rd &amp; Grantham School Rd</t>
+  </si>
+  <si>
+    <t>Church St</t>
+  </si>
+  <si>
+    <t>HT Vann Ln</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1548,11 +1560,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1568,10 +1581,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1861,7 +1870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C403"/>
+  <dimension ref="A1:C417"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -6302,7 +6311,162 @@
         <v>484</v>
       </c>
     </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A404" s="2">
+        <v>46024</v>
+      </c>
+      <c r="B404" t="s">
+        <v>491</v>
+      </c>
+      <c r="C404" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A405" s="2">
+        <v>46028</v>
+      </c>
+      <c r="B405" t="s">
+        <v>490</v>
+      </c>
+      <c r="C405" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A406" s="2">
+        <v>46032</v>
+      </c>
+      <c r="B406" t="s">
+        <v>401</v>
+      </c>
+      <c r="C406" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A407" s="2">
+        <v>46035</v>
+      </c>
+      <c r="B407" t="s">
+        <v>482</v>
+      </c>
+      <c r="C407" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A408" s="2">
+        <v>46038</v>
+      </c>
+      <c r="B408" t="s">
+        <v>379</v>
+      </c>
+      <c r="C408" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A409" s="2">
+        <v>46043</v>
+      </c>
+      <c r="B409" t="s">
+        <v>482</v>
+      </c>
+      <c r="C409" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A410" s="2">
+        <v>46050</v>
+      </c>
+      <c r="B410" t="s">
+        <v>393</v>
+      </c>
+      <c r="C410" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A411" s="2">
+        <v>46051</v>
+      </c>
+      <c r="B411" t="s">
+        <v>410</v>
+      </c>
+      <c r="C411" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A412" s="2">
+        <v>46053</v>
+      </c>
+      <c r="B412" t="s">
+        <v>389</v>
+      </c>
+      <c r="C412" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A413" s="2">
+        <v>46060</v>
+      </c>
+      <c r="B413" t="s">
+        <v>373</v>
+      </c>
+      <c r="C413" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A414" s="2">
+        <v>46073</v>
+      </c>
+      <c r="B414" t="s">
+        <v>492</v>
+      </c>
+      <c r="C414" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A415" s="2">
+        <v>46088</v>
+      </c>
+      <c r="B415" t="s">
+        <v>365</v>
+      </c>
+      <c r="C415" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A416" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B416" t="s">
+        <v>406</v>
+      </c>
+      <c r="C416" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A417" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B417" t="s">
+        <v>365</v>
+      </c>
+      <c r="C417" t="s">
+        <v>484</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>